--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260817.xlsx
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>5,759,000</t>
+          <t>5,792,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9,937,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>9,852,000</t>
+          <t>21,281,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>6,021,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -689,44 +689,44 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>47,420,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>47,068,000</t>
+          <t>35,599,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>9,871,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>20,089,000</t>
+          <t>20,234,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -787,188 +787,188 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>3,829,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>35,274,000</t>
+          <t>11,265,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>3,748,441,033</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>11,165,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>26,121,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>34,668,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>31,215,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,346,403,838</t>
+          <t>6,538,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -985,78 +985,78 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>4,161,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>2,845,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>34,072,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>20,776,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,169,000</t>
+          <t>2,187,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1095,29 +1095,29 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,470,000</t>
+          <t>9,548,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>3,897,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>15,188,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,149 +1151,149 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>17,521,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,634,625,322</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>2,647,281,747</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>6,600,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>14,241,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>6,023,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>4,928,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>14,245,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1381,95 +1381,95 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>23,751,004</t>
+          <t>23,917,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>23,400,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>13,914,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>3,529,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>8,785,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>7,285,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1535,122 +1535,122 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>8,951,000</t>
+          <t>9,042,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>2,113,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,918,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>47,579,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>49,379,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>6,399,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>16,762,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,174,000</t>
+          <t>18,334,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>17,187,000</t>
+          <t>17,362,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-30,947,675</t>
+          <t>-151,864,896</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
     </row>
